--- a/events/DeepCreek_2014_WCH/DeepCreek_2014_WCH_start.xlsx
+++ b/events/DeepCreek_2014_WCH/DeepCreek_2014_WCH_start.xlsx
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="J23" t="n">
